--- a/cuadros/MAYO/CENTRAL.xlsx
+++ b/cuadros/MAYO/CENTRAL.xlsx
@@ -1,33 +1,76 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>SUCURSAL</t>
+  </si>
+  <si>
+    <t>PROVEEDOR</t>
+  </si>
+  <si>
+    <t>FACTURA</t>
+  </si>
+  <si>
+    <t>FECHA</t>
+  </si>
+  <si>
+    <t>TIPO FISCALIZACIÓN</t>
+  </si>
+  <si>
+    <t>RESPONSABLE</t>
+  </si>
+  <si>
+    <t>INCIDENCIA</t>
+  </si>
+  <si>
+    <t>TIPO DE ERROR</t>
+  </si>
+  <si>
+    <t>OBSERVACIÓN</t>
+  </si>
+  <si>
+    <t>MONTO $</t>
+  </si>
+  <si>
+    <t>F COBRADA</t>
+  </si>
+  <si>
+    <t>CLASIFICACIÓN MONTO</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,80 +89,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -407,142 +383,49 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>SUCURSAL</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>PROVEEDOR</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>FACTURA</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>TIPO DE FISCALIZACION</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>INCIDENCIA</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>TIPO DE ERROR</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>OBSERVACIONES</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>F COBRADA</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HIST_20260501_0</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>mimesa</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>10101</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>RECEPCION</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>genesis montero</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>NO SE INDICÓ DIFERENCIA AL DORSO DE LA FACTURA.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>TIPO D</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>kkkkkkk</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>RECUPERACIÓN</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>20</v>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/CENTRAL.xlsx
+++ b/cuadros/MAYO/CENTRAL.xlsx
@@ -1,76 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>SUCURSAL</t>
-  </si>
-  <si>
-    <t>PROVEEDOR</t>
-  </si>
-  <si>
-    <t>FACTURA</t>
-  </si>
-  <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t>TIPO FISCALIZACIÓN</t>
-  </si>
-  <si>
-    <t>RESPONSABLE</t>
-  </si>
-  <si>
-    <t>INCIDENCIA</t>
-  </si>
-  <si>
-    <t>TIPO DE ERROR</t>
-  </si>
-  <si>
-    <t>OBSERVACIÓN</t>
-  </si>
-  <si>
-    <t>MONTO $</t>
-  </si>
-  <si>
-    <t>F COBRADA</t>
-  </si>
-  <si>
-    <t>CLASIFICACIÓN MONTO</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -89,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -383,49 +407,79 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SUCURSAL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TIPO FISCALIZACIÓN</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>INCIDENCIA</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TIPO DE ERROR</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>OBSERVACIÓN</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MONTO $</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>F COBRADA</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>CLASIFICACIÓN MONTO</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/CENTRAL.xlsx
+++ b/cuadros/MAYO/CENTRAL.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -49,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -412,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,8 +482,335 @@
           <t>ID</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>FOTO_INCIDENCIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>YEFFERSON MORGADO</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>126015</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Génesis Montero </t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>DOCUMENTO NO LEGIBLE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>LUEGO DE CULMINAR LA RECEPCION NO FUE ENVIADA LA FACTURA CON LAS CANTIDADES QUE FUERON RECIBIDAS</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>ID_20260513163507</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yeferson Morgado </t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>126014</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Génesis Montero </t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>DOCUMENTO NO LEGIBLE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>LUEGO DE CULMINAR LA RECEPCION NO FUE ENVIADA LA FACTURA CON LAS CANTIDADES QUE FUERON RECIBIDAS</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ID_20260513163559</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GRUPO LP2024, C.A</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PETER ARANDA</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DOCUMENTO NO LEGIBLE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LUEGO DE CULMINAR LA RECEPCION NO FUE ENVIADA LA FACTURA CON LAS CANTIDADES QUE FUERON RECIBIDAS</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ID_20260513163804</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GRUPO LP2024, C.A</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PETER ARANDA</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>DOCUMENTO NO LEGIBLE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LUEGO DE CULMINAR LA RECEPCION NO FUE ENVIADA LA FACTURA CON LAS CANTIDADES QUE FUERON RECIBIDAS</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ID_20260513163931</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GRUPO LP2024, C.A</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>000008</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PETER ARANDA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>DOCUMENTO NO LEGIBLE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LUEGO DE CULMINAR LA RECEPCION NO FUE ENVIADA LA FACTURA CON LAS CANTIDADES QUE FUERON RECIBIDAS</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ID_20260513164028</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/CENTRAL.xlsx
+++ b/cuadros/MAYO/CENTRAL.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="57">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -73,6 +73,9 @@
     <t>INVERSIONES VELANDRIA</t>
   </si>
   <si>
+    <t xml:space="preserve">DISTRIBUIDORA AGRICOLA CORVARA </t>
+  </si>
+  <si>
     <t>D007321</t>
   </si>
   <si>
@@ -85,12 +88,27 @@
     <t>D007319</t>
   </si>
   <si>
+    <t>031110</t>
+  </si>
+  <si>
+    <t>031111</t>
+  </si>
+  <si>
+    <t>031114</t>
+  </si>
+  <si>
+    <t>031109</t>
+  </si>
+  <si>
     <t>2026-05-04</t>
   </si>
   <si>
     <t>2026-05-05</t>
   </si>
   <si>
+    <t>2026-05-13</t>
+  </si>
+  <si>
     <t>RECEPCION</t>
   </si>
   <si>
@@ -155,6 +173,18 @@
   </si>
   <si>
     <t>ID_20260513165650</t>
+  </si>
+  <si>
+    <t>ID_20260513165907</t>
+  </si>
+  <si>
+    <t>ID_20260513165959</t>
+  </si>
+  <si>
+    <t>ID_20260513170037</t>
+  </si>
+  <si>
+    <t>ID_20260513170112</t>
   </si>
 </sst>
 </file>
@@ -486,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -544,34 +574,34 @@
         <v>126015</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -585,34 +615,34 @@
         <v>126014</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -626,34 +656,34 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -667,34 +697,34 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -708,34 +738,34 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -746,37 +776,37 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I7" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -787,37 +817,37 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L8" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -828,37 +858,37 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I9" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L9" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -869,37 +899,201 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>42</v>
+      </c>
+      <c r="L10" t="s">
+        <v>43</v>
+      </c>
+      <c r="M10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
         <v>24</v>
       </c>
-      <c r="E10" t="s">
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>42</v>
+      </c>
+      <c r="L11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
         <v>25</v>
       </c>
-      <c r="F10" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="D12" t="s">
         <v>30</v>
       </c>
-      <c r="H10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" t="s">
         <v>35</v>
       </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" t="s">
-        <v>36</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="H12" t="s">
         <v>37</v>
       </c>
-      <c r="M10" t="s">
-        <v>46</v>
+      <c r="I12" t="s">
+        <v>39</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
+        <v>42</v>
+      </c>
+      <c r="L12" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
+        <v>42</v>
+      </c>
+      <c r="L13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" t="s">
+        <v>39</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>42</v>
+      </c>
+      <c r="L14" t="s">
+        <v>43</v>
+      </c>
+      <c r="M14" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
